--- a/03_BOM/DAL_PDU_V1.0.xlsx
+++ b/03_BOM/DAL_PDU_V1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKING\SpaceLiinTech\SpaceLiinTech_BEE_DAL_PDU_HW_V1.0\03_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Altium_WorkSpace\1_Nanorack_DAL\SpaceLiinTech_BEE_DAL_PDU_HW_V1.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D952D6-7EB1-4F5A-82D8-A4FAB730A034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0F89BF-5696-4752-A226-A520763FA83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0934E210-AE90-4224-AA97-7F91D8D22FBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0934E210-AE90-4224-AA97-7F91D8D22FBF}"/>
   </bookViews>
   <sheets>
     <sheet name="DAL_PDU_V1.0" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="249">
   <si>
     <t>Name</t>
   </si>
@@ -347,21 +347,12 @@
     <t>53261-0671</t>
   </si>
   <si>
-    <t>2N7002</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
     <t>SOT-23</t>
   </si>
   <si>
-    <t>onsemi</t>
-  </si>
-  <si>
-    <t>2N7002KT1G</t>
-  </si>
-  <si>
     <t>499k</t>
   </si>
   <si>
@@ -494,9 +485,6 @@
     <t>R25</t>
   </si>
   <si>
-    <t>RC0603FR-071K43L</t>
-  </si>
-  <si>
     <t>49.9k</t>
   </si>
   <si>
@@ -792,19 +780,34 @@
   </si>
   <si>
     <t>Littelfuse Inc.</t>
+  </si>
+  <si>
+    <t>AO3400</t>
+  </si>
+  <si>
+    <t>Alpha &amp; Omega Semiconductor Inc.</t>
+  </si>
+  <si>
+    <t>RC0603FR-0743KL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFDFE2E7"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -848,12 +851,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1188,18 +1192,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36BFC9B8-6C78-4583-986B-2DF5614FFFBA}">
-  <dimension ref="A1:F71"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1239,7 +1243,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1259,7 +1263,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1299,7 +1303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1319,7 +1323,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1335,7 +1339,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1371,7 +1375,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
@@ -1391,7 +1395,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -1411,7 +1415,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>40</v>
       </c>
@@ -1431,7 +1435,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>43</v>
       </c>
@@ -1451,7 +1455,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1491,7 +1495,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>53</v>
       </c>
@@ -1505,13 +1509,13 @@
         <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>56</v>
       </c>
@@ -1525,13 +1529,13 @@
         <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>59</v>
       </c>
@@ -1547,7 +1551,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>61</v>
       </c>
@@ -1567,7 +1571,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>66</v>
       </c>
@@ -1587,7 +1591,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>69</v>
       </c>
@@ -1603,7 +1607,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>72</v>
       </c>
@@ -1619,7 +1623,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>75</v>
       </c>
@@ -1639,7 +1643,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>80</v>
       </c>
@@ -1659,7 +1663,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>85</v>
       </c>
@@ -1679,7 +1683,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>90</v>
       </c>
@@ -1695,7 +1699,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>93</v>
       </c>
@@ -1715,7 +1719,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>98</v>
       </c>
@@ -1735,856 +1739,857 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1">
         <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C32" s="1">
         <v>18</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C33" s="1">
         <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="C35" s="1">
         <v>2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C37" s="1">
         <v>2</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="1">
         <v>2</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B39" s="2" t="s">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="1">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C41" s="1">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="G43" s="5"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C45" s="1">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C46" s="1">
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C49" s="1">
         <v>22</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C50" s="1">
         <v>2</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="C52" s="1">
         <v>5</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C53" s="1">
         <v>2</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C54" s="1">
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B55" s="2" t="s">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="C56" s="1">
         <v>2</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F56" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="B57" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C58" s="1">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="F59" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2" t="s">
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B60" s="2" t="s">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C60" s="1">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="C61" s="1">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="E61" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C61" s="1">
-        <v>1</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+      <c r="F62" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C62" s="1">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2" t="s">
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E63" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C63" s="1">
-        <v>1</v>
-      </c>
-      <c r="D63" s="2" t="s">
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E65" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C64" s="1">
-        <v>1</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C65" s="1">
-        <v>1</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="E66" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66" s="2" t="s">
+      <c r="E67" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="B68" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C67" s="1">
-        <v>1</v>
-      </c>
-      <c r="D67" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="F68" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C68" s="1">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C69" s="1">
-        <v>1</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F69" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B70" s="2" t="s">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C70" s="1">
-        <v>1</v>
-      </c>
-      <c r="D70" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="C71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>